--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/ARIZONA_2011.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2011/ARIZONA_2011.xlsx
@@ -2461,7 +2461,7 @@
         <v>109</v>
       </c>
       <c r="D117">
-        <v>0.009575683036106</v>
+        <v>0.009575683036106002</v>
       </c>
     </row>
     <row r="118">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C129">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C201">
@@ -11011,7 +11011,7 @@
         <v>109</v>
       </c>
       <c r="D592">
-        <v>0.009575683036106</v>
+        <v>0.009575683036106002</v>
       </c>
     </row>
     <row r="593">
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B633" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C633">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C676">
@@ -18312,7 +18312,7 @@
       </c>
       <c r="B998" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C998">
